--- a/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/01_SW1 - Standart İş, İş Yeri ve Görsel Yönetim/EKG-URT-LST-01_kontaminasyon_risk_alanlari_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/07_Standart İş ve Uygunsuz Ürün/01_SW1 - Standart İş, İş Yeri ve Görsel Yönetim/EKG-URT-LST-01_kontaminasyon_risk_alanlari_listesi.xlsx
@@ -818,7 +818,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-LST-01&amp;C&amp;"Arial,Regular"&amp;11Kontaminasyon Risk Alanları Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: S/O/D/AP tekrarları çıkarıldı; fiili alan, kirlilik kaynağı, önlem, sorumlu ve kontrol kaydı odaklı liste kuruldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>